--- a/AAII_Financials/Yearly/IVV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IVV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>IVV</t>
   </si>
@@ -1593,7 +1593,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2125500</v>
       </c>
       <c r="E42" s="3">
         <v>4406500</v>
@@ -1713,7 +1713,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>525100</v>
+        <v>2650700</v>
       </c>
       <c r="E46" s="3">
         <v>4806200</v>
@@ -1743,7 +1743,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>720657100</v>
+        <v>717511700</v>
       </c>
       <c r="E47" s="3">
         <v>576843900</v>
@@ -1892,8 +1892,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3">
+        <v>1019900</v>
       </c>
       <c r="E52" s="3">
         <v>3306700</v>
@@ -2070,8 +2070,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>7100</v>
       </c>
       <c r="E59" s="3">
         <v>1200</v>
@@ -2101,7 +2101,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1023400</v>
+        <v>1030500</v>
       </c>
       <c r="E60" s="3">
         <v>3405200</v>
@@ -2160,8 +2160,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>7100</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>5</v>
